--- a/mode_docx_nc/pmi_gz/gzotkl_modes/ГЗоткл_8.xlsx
+++ b/mode_docx_nc/pmi_gz/gzotkl_modes/ГЗоткл_8.xlsx
@@ -437,251 +437,302 @@
   </sheetPr>
   <dimension ref="A1:AW2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="26" max="26"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="20" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="33" max="33"/>
+    <col width="20" customWidth="1" min="34" max="34"/>
+    <col width="20" customWidth="1" min="35" max="35"/>
+    <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_oilptrc1_apttechlgc</t>
+          <t>APTTECHLGC_1_OILPTRC1_EnaDis</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_oilptrc1_apttechlgc</t>
+          <t>APTTECHLGC_1_OILPTRC1_LowIsolTripCtrl</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_winptrc1_apttechlgc</t>
+          <t>APTTECHLGC_1_WINPTRC1_EnaDis</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_winptrc1_apttechlgc</t>
+          <t>APTTECHLGC_1_WINPTRC1_LowIsolTripCtrl</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_vlvptrc1_apttechlgc</t>
+          <t>APTTECHLGC_1_VLVPTRC1_EnaDis</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_vlvptrc1_apttechlgc</t>
+          <t>APTTECHLGC_1_VLVPTRC1_LowIsolTripCtrl</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_prvlvptrc1_almtechlgc</t>
+          <t>ALMTECHLGC_UIRZ_1_PRVLVPTRC1_EnaDis</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_shvlvptrc1_almtechlgc</t>
+          <t>ALMTECHLGC_UIRZ_1_SHVLVPTRC1_EnaDis</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_levptrc1_almtechlgc</t>
+          <t>ALMTECHLGC_UIRZ_1_LEVPTRC1_EnaDis</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_talmgaslgc</t>
+          <t>TALMGASLGC_1_PTRC1_EnaDis</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptrc1_talmgaslgc</t>
+          <t>TALMGASLGC_1_PTRC1_LowIsolSignCtrl</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_ttrgaslgc</t>
+          <t>TTRGASLGC_1_PTRC1_EnaDis</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptrc1_ttrgaslgc</t>
+          <t>TTRGASLGC_1_PTRC1_LowIsolTripCtrl</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_tltcgaslgc</t>
+          <t>TLTCGASLGC_1_PTRC1_EnaDis</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptrc1_tltcgaslgc</t>
+          <t>TLTCGASLGC_1_PTRC1_LowIsolTripCtrl</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptrc1_tofflvlgc</t>
+          <t>TOFFLVLGC_1_PTRC1_EnaDis</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rbre1_tofflvlgc</t>
+          <t>TOFFLVLGC_1_RBRE1_EnaDis</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_rbre1_tofflvlgc</t>
+          <t>TOFFLVLGC_1_RBRE1_PVOC2_Ctrl</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_rbre1_tofflvlgc</t>
+          <t>TOFFLVLGC_1_RBRE1_PVOC3_Ctrl</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvcbrblc1_tofflvlgc</t>
+          <t>TOFFLVLGC_1_LVCBRBLC1_EnaDis</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_lvcbrblc1_tofflvlgc</t>
+          <t>TOFFLVLGC_1_LVCBRBLC1_PVOC2_Ctrl</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_lvcbrblc1_tofflvlgc</t>
+          <t>TOFFLVLGC_1_LVCBRBLC1_PVOC3_Ctrl</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvalh</t>
+          <t>T_LVALH_1_CALH1_GASSign_Ctl</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_lvalh</t>
+          <t>T_LVALH_1_CALH1_LowIsolGAS_Ctl</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_lvalh</t>
+          <t>T_LVALH_1_CALH1_GASBlock_Ctl</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_lvalh</t>
+          <t>T_LVALH_1_CALH1_TECHSign_Ctl</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_lvalh</t>
+          <t>T_LVALH_1_CALH1_LowIsolTECH_Ctl</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_lvalh</t>
+          <t>T_LVALH_1_CALH1_TECHBlock_Ctl</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>SGF7_lvalh</t>
+          <t>T_LVALH_1_CALH1_ALMSign_Ctl</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>SGF8_lvalh</t>
+          <t>T_LVALH_1_CALH1_OCSign_Ctl</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>SGF9_lvalh</t>
+          <t>T_LVALH_1_CALH1_OCnnSign_Ctl</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>SGF10_lvalh</t>
+          <t>T_LVALH_1_CALH1_OpExt_Ctl</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>SGF11_lvalh</t>
+          <t>T_LVALH_1_CALH1_CtlCir_Ctl</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>SGF12_lvalh</t>
+          <t>T_LVALH_1_CALH1_TestBlock_Ctl</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_lvalh</t>
+          <t>T_LVALH_1_CALH1_SwOperExcTim_Ctl</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>SGF14_lvalh</t>
+          <t>T_LVALH_1_CALH1_ExtSignGen_Ctl</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_tsa</t>
+          <t>T_SignAssembly_1_Ctl_SA1</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_tsa</t>
+          <t>T_SignAssembly_1_Ctl_SA2</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_tsa</t>
+          <t>T_SignAssembly_1_Ctl_SA3</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_tsa</t>
+          <t>T_SignAssembly_1_Ctl_SA4</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_tsa</t>
+          <t>T_SignAssembly_1_Ctl_SA5</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_tsa</t>
+          <t>T_SignAssembly_1_Ctl_SG1</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>SGF7_tsa</t>
+          <t>T_SignAssembly_1_Ctl_SG2</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>SGF8_tsa</t>
+          <t>T_SignAssembly_1_Ctl_GAS_OCControl</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>SGF9_tsa</t>
+          <t>T_SignAssembly_1_Ctl_TECH_OCControl</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>SGF10_tsa</t>
+          <t>T_SignAssembly_1_Ctl_OCcir_CB</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>SGF11_tsa</t>
+          <t>T_SignAssembly_1_Ctl_ARCnn_OCControl</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>SGF12_tsa</t>
+          <t>T_SignAssembly_1_Ctl_CBFPnn_OCControl</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>SGF13_tsa</t>
+          <t>T_SignAssembly_1_Ctl_IEDvt_OCControl</t>
         </is>
       </c>
     </row>
@@ -719,7 +770,7 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
@@ -731,25 +782,25 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
@@ -857,22 +908,22 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>T1_apttechlgc</t>
+          <t>APTTECHLGC_1_LLN0_TopOnBlk</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptrc1_talmgaslgc</t>
+          <t>TALMGASLGC_1_PTRC1_TopOnBlk</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>T1_ttrgaslgc</t>
+          <t>TTRGASLGC_1_LLN0_TopOnBlk</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>T1_tltcgaslgc</t>
+          <t>TLTCGASLGC_1_LLN0_TopOnBlk</t>
         </is>
       </c>
     </row>
@@ -2008,86 +2059,86 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AO2" s="2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" s="2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BA2" s="2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="BE2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2103,9 +2154,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BH2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="BI2" s="2" t="inlineStr">
